--- a/data/nzd0078/nzd0078.xlsx
+++ b/data/nzd0078/nzd0078.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I343"/>
+  <dimension ref="A1:I345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11759,6 +11759,72 @@
         <v>343.18</v>
       </c>
       <c r="I343" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>350.18</v>
+      </c>
+      <c r="C344" t="n">
+        <v>349.18</v>
+      </c>
+      <c r="D344" t="n">
+        <v>355.32</v>
+      </c>
+      <c r="E344" t="n">
+        <v>346.56</v>
+      </c>
+      <c r="F344" t="n">
+        <v>348.85</v>
+      </c>
+      <c r="G344" t="n">
+        <v>351.77</v>
+      </c>
+      <c r="H344" t="n">
+        <v>344.49</v>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>350.69</v>
+      </c>
+      <c r="C345" t="n">
+        <v>349.14</v>
+      </c>
+      <c r="D345" t="n">
+        <v>354.79</v>
+      </c>
+      <c r="E345" t="n">
+        <v>346.2</v>
+      </c>
+      <c r="F345" t="n">
+        <v>347.69</v>
+      </c>
+      <c r="G345" t="n">
+        <v>350.73</v>
+      </c>
+      <c r="H345" t="n">
+        <v>348.14</v>
+      </c>
+      <c r="I345" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11775,7 +11841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B346"/>
+  <dimension ref="A1:B348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15238,6 +15304,26 @@
       </c>
       <c r="B346" t="n">
         <v>-0.39</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -15406,28 +15492,28 @@
         <v>0.1223</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4525785375067692</v>
+        <v>0.4569377139179629</v>
       </c>
       <c r="J2" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K2" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3134873572461533</v>
+        <v>0.3195606413245935</v>
       </c>
       <c r="M2" t="n">
-        <v>3.857087921134506</v>
+        <v>3.851969767490965</v>
       </c>
       <c r="N2" t="n">
-        <v>24.25436186302789</v>
+        <v>24.19685363572604</v>
       </c>
       <c r="O2" t="n">
-        <v>4.924871761074383</v>
+        <v>4.919029745358941</v>
       </c>
       <c r="P2" t="n">
-        <v>334.7194003517737</v>
+        <v>334.6735756113781</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15484,28 +15570,28 @@
         <v>0.1217</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5024270777689701</v>
+        <v>0.5045583131076713</v>
       </c>
       <c r="J3" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K3" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3796684072013993</v>
+        <v>0.3843732102540774</v>
       </c>
       <c r="M3" t="n">
-        <v>3.72883727149662</v>
+        <v>3.717381934677068</v>
       </c>
       <c r="N3" t="n">
-        <v>22.30175027129753</v>
+        <v>22.19197105911592</v>
       </c>
       <c r="O3" t="n">
-        <v>4.722472897889148</v>
+        <v>4.710835494805132</v>
       </c>
       <c r="P3" t="n">
-        <v>334.0811623455529</v>
+        <v>334.058759126228</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15562,28 +15648,28 @@
         <v>0.0936</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4298645144235045</v>
+        <v>0.433724181142157</v>
       </c>
       <c r="J4" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K4" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2372067342865909</v>
+        <v>0.2423441166827259</v>
       </c>
       <c r="M4" t="n">
-        <v>3.853204301966867</v>
+        <v>3.842970337571988</v>
       </c>
       <c r="N4" t="n">
-        <v>32.13042431518087</v>
+        <v>32.00925279682252</v>
       </c>
       <c r="O4" t="n">
-        <v>5.668370516751783</v>
+        <v>5.657672029803646</v>
       </c>
       <c r="P4" t="n">
-        <v>340.3743925057616</v>
+        <v>340.3338216469097</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15640,28 +15726,28 @@
         <v>0.1175</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4012626513306886</v>
+        <v>0.4019999398846781</v>
       </c>
       <c r="J5" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K5" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3078427503416338</v>
+        <v>0.3112405989988347</v>
       </c>
       <c r="M5" t="n">
-        <v>3.321958291029655</v>
+        <v>3.305251499844189</v>
       </c>
       <c r="N5" t="n">
-        <v>19.57522456260415</v>
+        <v>19.4639965672538</v>
       </c>
       <c r="O5" t="n">
-        <v>4.424389739004029</v>
+        <v>4.411801963739284</v>
       </c>
       <c r="P5" t="n">
-        <v>335.1858108178477</v>
+        <v>335.1780616138083</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15718,28 +15804,28 @@
         <v>0.1334</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5051296211536928</v>
+        <v>0.5031679798190908</v>
       </c>
       <c r="J6" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K6" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4393913239588688</v>
+        <v>0.4402539024791152</v>
       </c>
       <c r="M6" t="n">
-        <v>3.139212377375998</v>
+        <v>3.133062951642899</v>
       </c>
       <c r="N6" t="n">
-        <v>17.60303064549225</v>
+        <v>17.51953592896231</v>
       </c>
       <c r="O6" t="n">
-        <v>4.195596578019894</v>
+        <v>4.185634471494412</v>
       </c>
       <c r="P6" t="n">
-        <v>336.7037147379716</v>
+        <v>336.7243388459854</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15796,28 +15882,28 @@
         <v>0.1117</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5715664225017854</v>
+        <v>0.57100538764649</v>
       </c>
       <c r="J7" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K7" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4477901347962024</v>
+        <v>0.4503279883903565</v>
       </c>
       <c r="M7" t="n">
-        <v>3.836774063806453</v>
+        <v>3.818097100313729</v>
       </c>
       <c r="N7" t="n">
-        <v>21.78394286405232</v>
+        <v>21.66026881401662</v>
       </c>
       <c r="O7" t="n">
-        <v>4.667327164882737</v>
+        <v>4.654059390899156</v>
       </c>
       <c r="P7" t="n">
-        <v>336.7120993523524</v>
+        <v>336.7180000267408</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15874,28 +15960,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4456871564273488</v>
+        <v>0.4431768276353874</v>
       </c>
       <c r="J8" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K8" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2306615021254923</v>
+        <v>0.2306164223498763</v>
       </c>
       <c r="M8" t="n">
-        <v>4.915791682127195</v>
+        <v>4.898281384808321</v>
       </c>
       <c r="N8" t="n">
-        <v>35.82416047862907</v>
+        <v>35.6628064268733</v>
       </c>
       <c r="O8" t="n">
-        <v>5.985328769468647</v>
+        <v>5.971834427282232</v>
       </c>
       <c r="P8" t="n">
-        <v>336.7975356877972</v>
+        <v>336.8239131898439</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -15933,7 +16019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I343"/>
+  <dimension ref="A1:I345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32057,6 +32143,100 @@
         </is>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>-35.45435976874497,174.4279594002468</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>-35.45509985805025,174.4281260956754</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>-35.45571071126577,174.42864457366372</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>-35.45628350786904,174.42923900491573</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>-35.45673222961544,174.42997843645134</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>-35.45703564647781,174.4308078445989</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>-35.4572106092418,174.43170338847503</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>-35.4543588541762,174.4279649069711</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>-35.45509998770878,174.42812568443912</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>-35.45571371489749,174.42864003238446</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>-35.4562859742723,174.42923642692037</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>-35.456741109597885,174.42997168658002</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>-35.45704462736714,174.43080455523588</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>-35.45717801246899,174.43170887412722</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0078/nzd0078.xlsx
+++ b/data/nzd0078/nzd0078.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I345"/>
+  <dimension ref="A1:I346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11827,6 +11827,39 @@
       <c r="I345" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>350.24</v>
+      </c>
+      <c r="C346" t="n">
+        <v>349</v>
+      </c>
+      <c r="D346" t="n">
+        <v>354.4</v>
+      </c>
+      <c r="E346" t="n">
+        <v>345.96</v>
+      </c>
+      <c r="F346" t="n">
+        <v>347.28</v>
+      </c>
+      <c r="G346" t="n">
+        <v>350.22</v>
+      </c>
+      <c r="H346" t="n">
+        <v>348.47</v>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B348"/>
+  <dimension ref="A1:B349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15324,6 +15357,16 @@
       </c>
       <c r="B348" t="n">
         <v>-0.49</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -15492,28 +15535,28 @@
         <v>0.1223</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4569377139179629</v>
+        <v>0.4589405241043222</v>
       </c>
       <c r="J2" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K2" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3195606413245935</v>
+        <v>0.3224890494471713</v>
       </c>
       <c r="M2" t="n">
-        <v>3.851969767490965</v>
+        <v>3.84869876056917</v>
       </c>
       <c r="N2" t="n">
-        <v>24.19685363572604</v>
+        <v>24.16218291261506</v>
       </c>
       <c r="O2" t="n">
-        <v>4.919029745358941</v>
+        <v>4.915504339598843</v>
       </c>
       <c r="P2" t="n">
-        <v>334.6735756113781</v>
+        <v>334.6524496743182</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15570,28 +15613,28 @@
         <v>0.1217</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5045583131076713</v>
+        <v>0.5054926194247881</v>
       </c>
       <c r="J3" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K3" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3843732102540774</v>
+        <v>0.3866256038523244</v>
       </c>
       <c r="M3" t="n">
-        <v>3.717381934677068</v>
+        <v>3.711069255544268</v>
       </c>
       <c r="N3" t="n">
-        <v>22.19197105911592</v>
+        <v>22.13536442024015</v>
       </c>
       <c r="O3" t="n">
-        <v>4.710835494805132</v>
+        <v>4.704823527002915</v>
       </c>
       <c r="P3" t="n">
-        <v>334.058759126228</v>
+        <v>334.0489039254783</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15648,28 +15691,28 @@
         <v>0.0936</v>
       </c>
       <c r="I4" t="n">
-        <v>0.433724181142157</v>
+        <v>0.4352200733412283</v>
       </c>
       <c r="J4" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K4" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2423441166827259</v>
+        <v>0.2446324884565064</v>
       </c>
       <c r="M4" t="n">
-        <v>3.842970337571988</v>
+        <v>3.836771947109747</v>
       </c>
       <c r="N4" t="n">
-        <v>32.00925279682252</v>
+        <v>31.93625671416072</v>
       </c>
       <c r="O4" t="n">
-        <v>5.657672029803646</v>
+        <v>5.651217277203268</v>
       </c>
       <c r="P4" t="n">
-        <v>340.3338216469097</v>
+        <v>340.3180427554995</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15726,28 +15769,28 @@
         <v>0.1175</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4019999398846781</v>
+        <v>0.4021035666330326</v>
       </c>
       <c r="J5" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K5" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3112405989988347</v>
+        <v>0.3126717081057222</v>
       </c>
       <c r="M5" t="n">
-        <v>3.305251499844189</v>
+        <v>3.296033048926094</v>
       </c>
       <c r="N5" t="n">
-        <v>19.4639965672538</v>
+        <v>19.40767412938206</v>
       </c>
       <c r="O5" t="n">
-        <v>4.411801963739284</v>
+        <v>4.405414183636092</v>
       </c>
       <c r="P5" t="n">
-        <v>335.1780616138083</v>
+        <v>335.176968543592</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15804,28 +15847,28 @@
         <v>0.1334</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5031679798190908</v>
+        <v>0.5016219206730607</v>
       </c>
       <c r="J6" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K6" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4402539024791152</v>
+        <v>0.4399565040879264</v>
       </c>
       <c r="M6" t="n">
-        <v>3.133062951642899</v>
+        <v>3.133470042367853</v>
       </c>
       <c r="N6" t="n">
-        <v>17.51953592896231</v>
+        <v>17.48988827228636</v>
       </c>
       <c r="O6" t="n">
-        <v>4.185634471494412</v>
+        <v>4.182091375410915</v>
       </c>
       <c r="P6" t="n">
-        <v>336.7243388459854</v>
+        <v>336.7406469057468</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15882,28 +15925,28 @@
         <v>0.1117</v>
       </c>
       <c r="I7" t="n">
-        <v>0.57100538764649</v>
+        <v>0.5701205821614223</v>
       </c>
       <c r="J7" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K7" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4503279883903565</v>
+        <v>0.4510050709488493</v>
       </c>
       <c r="M7" t="n">
-        <v>3.818097100313729</v>
+        <v>3.812395341260232</v>
       </c>
       <c r="N7" t="n">
-        <v>21.66026881401662</v>
+        <v>21.60440719398861</v>
       </c>
       <c r="O7" t="n">
-        <v>4.654059390899156</v>
+        <v>4.648054129847092</v>
       </c>
       <c r="P7" t="n">
-        <v>336.7180000267408</v>
+        <v>336.7273330854175</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15960,28 +16003,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4431768276353874</v>
+        <v>0.4431546439209554</v>
       </c>
       <c r="J8" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K8" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2306164223498763</v>
+        <v>0.2316928261843886</v>
       </c>
       <c r="M8" t="n">
-        <v>4.898281384808321</v>
+        <v>4.884180158328133</v>
       </c>
       <c r="N8" t="n">
-        <v>35.6628064268733</v>
+        <v>35.55944032447075</v>
       </c>
       <c r="O8" t="n">
-        <v>5.971834427282232</v>
+        <v>5.963173678878618</v>
       </c>
       <c r="P8" t="n">
-        <v>336.8239131898439</v>
+        <v>336.8241471869337</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16019,7 +16062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I345"/>
+  <dimension ref="A1:I346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32237,6 +32280,53 @@
         </is>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>-35.45435966114867,174.42796004809674</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>-35.45510044151366,174.42812424511214</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>-35.455715925116955,174.42863669068817</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>-35.4562876185411,174.4292347082567</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>-35.456744248212274,174.42996930084925</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-35.45704903145707,174.43080294218262</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>-35.45717506536347,174.43170937009012</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0078/nzd0078.xlsx
+++ b/data/nzd0078/nzd0078.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I346"/>
+  <dimension ref="A1:I347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11860,6 +11860,39 @@
       <c r="I346" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>347.72</v>
+      </c>
+      <c r="C347" t="n">
+        <v>349.55</v>
+      </c>
+      <c r="D347" t="n">
+        <v>352.42</v>
+      </c>
+      <c r="E347" t="n">
+        <v>345.47</v>
+      </c>
+      <c r="F347" t="n">
+        <v>346.65</v>
+      </c>
+      <c r="G347" t="n">
+        <v>348.72</v>
+      </c>
+      <c r="H347" t="n">
+        <v>351.85</v>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11874,7 +11907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B349"/>
+  <dimension ref="A1:B350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15367,6 +15400,16 @@
       </c>
       <c r="B349" t="n">
         <v>0.71</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
@@ -15535,28 +15578,28 @@
         <v>0.1223</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4589405241043222</v>
+        <v>0.4594142686054291</v>
       </c>
       <c r="J2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3224890494471713</v>
+        <v>0.3243370550100014</v>
       </c>
       <c r="M2" t="n">
-        <v>3.84869876056917</v>
+        <v>3.839369840859994</v>
       </c>
       <c r="N2" t="n">
-        <v>24.16218291261506</v>
+        <v>24.09424747109345</v>
       </c>
       <c r="O2" t="n">
-        <v>4.915504339598843</v>
+        <v>4.908589152810963</v>
       </c>
       <c r="P2" t="n">
-        <v>334.6524496743182</v>
+        <v>334.6473810219821</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15613,28 +15656,28 @@
         <v>0.1217</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5054926194247881</v>
+        <v>0.5066615820422009</v>
       </c>
       <c r="J3" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K3" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3866256038523244</v>
+        <v>0.3891321750321045</v>
       </c>
       <c r="M3" t="n">
-        <v>3.711069255544268</v>
+        <v>3.705820972007585</v>
       </c>
       <c r="N3" t="n">
-        <v>22.13536442024015</v>
+        <v>22.08294211433709</v>
       </c>
       <c r="O3" t="n">
-        <v>4.704823527002915</v>
+        <v>4.699249101115741</v>
       </c>
       <c r="P3" t="n">
-        <v>334.0489039254783</v>
+        <v>334.0363970465853</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15691,28 +15734,28 @@
         <v>0.0936</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4352200733412283</v>
+        <v>0.4355016167940565</v>
       </c>
       <c r="J4" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K4" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2446324884565064</v>
+        <v>0.2460642875574452</v>
       </c>
       <c r="M4" t="n">
-        <v>3.836771947109747</v>
+        <v>3.826586740009352</v>
       </c>
       <c r="N4" t="n">
-        <v>31.93625671416072</v>
+        <v>31.84462554793912</v>
       </c>
       <c r="O4" t="n">
-        <v>5.651217277203268</v>
+        <v>5.64310424748109</v>
       </c>
       <c r="P4" t="n">
-        <v>340.3180427554995</v>
+        <v>340.3150304864883</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15769,28 +15812,28 @@
         <v>0.1175</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4021035666330326</v>
+        <v>0.4018434674287071</v>
       </c>
       <c r="J5" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K5" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3126717081057222</v>
+        <v>0.3137767720538015</v>
       </c>
       <c r="M5" t="n">
-        <v>3.296033048926094</v>
+        <v>3.288194004516543</v>
       </c>
       <c r="N5" t="n">
-        <v>19.40767412938206</v>
+        <v>19.3521545403671</v>
       </c>
       <c r="O5" t="n">
-        <v>4.405414183636092</v>
+        <v>4.399108380156949</v>
       </c>
       <c r="P5" t="n">
-        <v>335.176968543592</v>
+        <v>335.1797513778763</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15847,28 +15890,28 @@
         <v>0.1334</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5016219206730607</v>
+        <v>0.4995945603587338</v>
       </c>
       <c r="J6" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K6" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4399565040879264</v>
+        <v>0.4390624259299164</v>
       </c>
       <c r="M6" t="n">
-        <v>3.133470042367853</v>
+        <v>3.136613455214107</v>
       </c>
       <c r="N6" t="n">
-        <v>17.48988827228636</v>
+        <v>17.47408871552451</v>
       </c>
       <c r="O6" t="n">
-        <v>4.182091375410915</v>
+        <v>4.180201994584055</v>
       </c>
       <c r="P6" t="n">
-        <v>336.7406469057468</v>
+        <v>336.7623378901683</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15925,28 +15968,28 @@
         <v>0.1117</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5701205821614223</v>
+        <v>0.5682412898068212</v>
       </c>
       <c r="J7" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K7" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4510050709488493</v>
+        <v>0.4506268021133767</v>
       </c>
       <c r="M7" t="n">
-        <v>3.812395341260232</v>
+        <v>3.812434320312515</v>
       </c>
       <c r="N7" t="n">
-        <v>21.60440719398861</v>
+        <v>21.57182550655831</v>
       </c>
       <c r="O7" t="n">
-        <v>4.648054129847092</v>
+        <v>4.644547933497759</v>
       </c>
       <c r="P7" t="n">
-        <v>336.7273330854175</v>
+        <v>336.7474398720105</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16003,28 +16046,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4431546439209554</v>
+        <v>0.4450121459802651</v>
       </c>
       <c r="J8" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K8" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2316928261843886</v>
+        <v>0.2341950496194209</v>
       </c>
       <c r="M8" t="n">
-        <v>4.884180158328133</v>
+        <v>4.880533624897765</v>
       </c>
       <c r="N8" t="n">
-        <v>35.55944032447075</v>
+        <v>35.48583776333474</v>
       </c>
       <c r="O8" t="n">
-        <v>5.963173678878618</v>
+        <v>5.956999056851926</v>
       </c>
       <c r="P8" t="n">
-        <v>336.8241471869337</v>
+        <v>336.804273537466</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16062,7 +16105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I346"/>
+  <dimension ref="A1:I347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32327,6 +32370,53 @@
         </is>
       </c>
     </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>-35.454364180190886,174.42793283839825</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>-35.45509865870868,174.4281298996109</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>-35.455727146229755,174.4286197251504</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>-35.45629097558984,174.42923119931817</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>-35.45674907096115,174.42996563496996</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>-35.45706198466259,174.43079819790734</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>-35.45714487985848,174.43171444995045</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0078/nzd0078.xlsx
+++ b/data/nzd0078/nzd0078.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I347"/>
+  <dimension ref="A1:I349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11893,6 +11893,72 @@
       <c r="I347" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>349.77</v>
+      </c>
+      <c r="C348" t="n">
+        <v>348.31</v>
+      </c>
+      <c r="D348" t="n">
+        <v>350.79</v>
+      </c>
+      <c r="E348" t="n">
+        <v>345.06</v>
+      </c>
+      <c r="F348" t="n">
+        <v>345.64</v>
+      </c>
+      <c r="G348" t="n">
+        <v>348.01</v>
+      </c>
+      <c r="H348" t="n">
+        <v>355.68</v>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>349.66</v>
+      </c>
+      <c r="C349" t="n">
+        <v>350.41</v>
+      </c>
+      <c r="D349" t="n">
+        <v>354.99</v>
+      </c>
+      <c r="E349" t="n">
+        <v>348.3</v>
+      </c>
+      <c r="F349" t="n">
+        <v>351.25</v>
+      </c>
+      <c r="G349" t="n">
+        <v>353.35</v>
+      </c>
+      <c r="H349" t="n">
+        <v>345.45</v>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11907,7 +11973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B350"/>
+  <dimension ref="A1:B352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15410,6 +15476,26 @@
       </c>
       <c r="B350" t="n">
         <v>0.15</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -15578,28 +15664,28 @@
         <v>0.1223</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4594142686054291</v>
+        <v>0.4625938077568952</v>
       </c>
       <c r="J2" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K2" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3243370550100014</v>
+        <v>0.329821167012457</v>
       </c>
       <c r="M2" t="n">
-        <v>3.839369840859994</v>
+        <v>3.829148334154314</v>
       </c>
       <c r="N2" t="n">
-        <v>24.09424747109345</v>
+        <v>23.99872246174863</v>
       </c>
       <c r="O2" t="n">
-        <v>4.908589152810963</v>
+        <v>4.898849095629363</v>
       </c>
       <c r="P2" t="n">
-        <v>334.6473810219821</v>
+        <v>334.6132232556543</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15656,28 +15742,28 @@
         <v>0.1217</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5066615820422009</v>
+        <v>0.5086766639516587</v>
       </c>
       <c r="J3" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K3" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3891321750321045</v>
+        <v>0.3938445676897635</v>
       </c>
       <c r="M3" t="n">
-        <v>3.705820972007585</v>
+        <v>3.693823901951694</v>
       </c>
       <c r="N3" t="n">
-        <v>22.08294211433709</v>
+        <v>21.97956439825566</v>
       </c>
       <c r="O3" t="n">
-        <v>4.699249101115741</v>
+        <v>4.688236811238919</v>
       </c>
       <c r="P3" t="n">
-        <v>334.0363970465853</v>
+        <v>334.0147428684056</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15734,28 +15820,28 @@
         <v>0.0936</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4355016167940565</v>
+        <v>0.4365477889290666</v>
       </c>
       <c r="J4" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K4" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2460642875574452</v>
+        <v>0.24918888621575</v>
       </c>
       <c r="M4" t="n">
-        <v>3.826586740009352</v>
+        <v>3.814812199189365</v>
       </c>
       <c r="N4" t="n">
-        <v>31.84462554793912</v>
+        <v>31.69143610113009</v>
       </c>
       <c r="O4" t="n">
-        <v>5.64310424748109</v>
+        <v>5.629514730518971</v>
       </c>
       <c r="P4" t="n">
-        <v>340.3150304864883</v>
+        <v>340.3037794522032</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15812,28 +15898,28 @@
         <v>0.1175</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4018434674287071</v>
+        <v>0.4026871101861665</v>
       </c>
       <c r="J5" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K5" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3137767720538015</v>
+        <v>0.3172693659809395</v>
       </c>
       <c r="M5" t="n">
-        <v>3.288194004516543</v>
+        <v>3.27732002120131</v>
       </c>
       <c r="N5" t="n">
-        <v>19.3521545403671</v>
+        <v>19.25896820423348</v>
       </c>
       <c r="O5" t="n">
-        <v>4.399108380156949</v>
+        <v>4.388504096412976</v>
       </c>
       <c r="P5" t="n">
-        <v>335.1797513778763</v>
+        <v>335.1706788491688</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15890,28 +15976,28 @@
         <v>0.1334</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4995945603587338</v>
+        <v>0.4976291381777806</v>
       </c>
       <c r="J6" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K6" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4390624259299164</v>
+        <v>0.4394311800395809</v>
       </c>
       <c r="M6" t="n">
-        <v>3.136613455214107</v>
+        <v>3.136775409642874</v>
       </c>
       <c r="N6" t="n">
-        <v>17.47408871552451</v>
+        <v>17.43516183851695</v>
       </c>
       <c r="O6" t="n">
-        <v>4.180201994584055</v>
+        <v>4.175543298604022</v>
       </c>
       <c r="P6" t="n">
-        <v>336.7623378901683</v>
+        <v>336.7834366899819</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15968,28 +16054,28 @@
         <v>0.1117</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5682412898068212</v>
+        <v>0.5667500532205217</v>
       </c>
       <c r="J7" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K7" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4506268021133767</v>
+        <v>0.4519432498331492</v>
       </c>
       <c r="M7" t="n">
-        <v>3.812434320312515</v>
+        <v>3.807196725751195</v>
       </c>
       <c r="N7" t="n">
-        <v>21.57182550655831</v>
+        <v>21.49814938623204</v>
       </c>
       <c r="O7" t="n">
-        <v>4.644547933497759</v>
+        <v>4.636609686638723</v>
       </c>
       <c r="P7" t="n">
-        <v>336.7474398720105</v>
+        <v>336.7634452153999</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16046,28 +16132,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4450121459802651</v>
+        <v>0.4471196519325503</v>
       </c>
       <c r="J8" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K8" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2341950496194209</v>
+        <v>0.2373599619727421</v>
       </c>
       <c r="M8" t="n">
-        <v>4.880533624897765</v>
+        <v>4.883319601487119</v>
       </c>
       <c r="N8" t="n">
-        <v>35.48583776333474</v>
+        <v>35.45161018519541</v>
       </c>
       <c r="O8" t="n">
-        <v>5.956999056851926</v>
+        <v>5.954125476104396</v>
       </c>
       <c r="P8" t="n">
-        <v>336.804273537466</v>
+        <v>336.78166152163</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16105,7 +16191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I347"/>
+  <dimension ref="A1:I349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32417,6 +32503,100 @@
         </is>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>-35.454360503986365,174.42795497327228</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>-35.45510267812316,174.42811715128605</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>-35.455736383810795,174.42860575856778</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-35.456293784548905,174.42922826326736</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>-35.456756802669425,174.42995975792445</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-35.45706811584648,174.43079595228318</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>-35.45711067557291,174.43172020611942</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>-35.454360701246216,174.42795378554737</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>-35.45509587104947,174.4281387411903</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>-35.45571258145158,174.4286417460748</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-35.45627158691924,174.42925146522438</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-35.45671385723685,174.42999240169777</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-35.457022002434265,174.43081284189904</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>-35.45720203584404,174.4317048312771</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
